--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-07-22T05:04:13.372Z</t>
+    <t>2026-07-22T21:35:33.729Z</t>
   </si>
   <si>
     <t>Department of Conservation</t>
